--- a/updated_generic_infra_kpis.xlsx
+++ b/updated_generic_infra_kpis.xlsx
@@ -864,12 +864,12 @@
       </c>
       <c r="T3" s="10" t="inlineStr">
         <is>
-          <t>YES (via paired tiles)</t>
+          <t>YES (auto-computed ratio tile)</t>
         </is>
       </c>
       <c r="U3" s="9" t="inlineStr">
         <is>
-          <t>'Raw Netcool Alerts (24h)' tile + 'Correlated SN Events (24h)' tile + 'Alert Dedup Ratio' markdown with the formula (Raw − Correlated) / Raw × 100. Users read the two counts; the markdown explains the ratio. A single auto-computed ratio tile would require an Elastic Transform to denormalize both counts into one index (noted in the panel).</t>
+          <t>'Alert Dedup Ratio (24h, %)' metric tile — computed in a single tile via cross-index ES|QL: FROM .ds-bridge-alerts-netcool-default-*, .ds-logs-servicenow.event-default-* METADATA _index | STATS raw = COUNT(CASE(STARTS_WITH(_index, '.ds-bridge-alerts-netcool'), 1, null)), correlated = COUNT(CASE(STARTS_WITH(_index, '.ds-logs-servicenow.event'), 1, null)) | EVAL metric_val = ROUND((raw - correlated) * 100.0 / raw, 1). Companion 'Raw Netcool Alerts (24h)' + 'Correlated SN Events (24h)' tiles show the underlying counts.</t>
         </is>
       </c>
     </row>

--- a/updated_generic_infra_kpis.xlsx
+++ b/updated_generic_infra_kpis.xlsx
@@ -121,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -156,6 +156,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -553,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:U16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="24" customWidth="1" min="16" max="16"/>
@@ -1808,6 +1810,154 @@
       <c r="U12" s="9" t="inlineStr">
         <is>
           <t>'Coverage Gap Risk (%)' metric tile: % of monitored+operational CIs whose latest telemetry is older than 15 min. Companion 'Coverage Gap — Monitored CIs Not Reporting (&gt;15 min)' full-width datatable lists the specific CIs with columns: CI Name, Host, Data Center, Support Team, Stale (min), Last Seen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>Total Servers Monitored</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>Distinct servers reporting any metric</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>unique_count(host.name)</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Baseline fleet size — denominator for availability/coverage KPIs</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>Ported from Infra Dashboard Prototype (infra_dashbaord_prototype.ndjson)</t>
+        </is>
+      </c>
+      <c r="T13" s="10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="U13" s="9" t="inlineStr">
+        <is>
+          <t>'Total Servers Monitored' metric tile — COUNT_DISTINCT(host.name) across metrics-*.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>Servers Up</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
+        <is>
+          <t>Servers reporting metrics within the last 15 min</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>unique_count(host.name) where @timestamp &gt;= now-15m</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>Live fleet health — how many servers are alive right now</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>Ported from Infra Dashboard Prototype; 5m window widened to 15m to avoid false-'down' readings from agent restarts / ingest gaps</t>
+        </is>
+      </c>
+      <c r="T14" s="10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="U14" s="9" t="inlineStr">
+        <is>
+          <t>'Servers Up' metric tile — COUNT_DISTINCT(host.name) filtered @timestamp &gt;= NOW() - 15 minutes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>Servers Down</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
+        <is>
+          <t>Servers NOT reporting in the last 15 min</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>total_servers − servers_up</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Immediate operational alarm — hosts to investigate</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>Ported from Infra Dashboard Prototype; 5m window widened to 15m</t>
+        </is>
+      </c>
+      <c r="T15" s="10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="U15" s="9" t="inlineStr">
+        <is>
+          <t>'Servers Down' metric tile — computed in a single ES|QL: STATS total = COUNT_DISTINCT(host.name), up = COUNT_DISTINCT(CASE(@timestamp &gt;= NOW() - 15 minutes, host.name, null)) | EVAL metric_val = total - up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Servers Availability %</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>% of monitored servers up in the last 15 min</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>up / total</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Aggregate fleet-availability indicator — top-line SLA number</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>Ported and renamed from 'Fleet Availability %' in the Infra Dashboard Prototype (per team request); 5m → 15m window carried forward</t>
+        </is>
+      </c>
+      <c r="T16" s="10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="U16" s="9" t="inlineStr">
+        <is>
+          <t>'Servers Availability %' metric tile — returns a fraction and uses Kibana 'percent' format so the '%' sign renders on the tile.</t>
         </is>
       </c>
     </row>

--- a/updated_generic_infra_kpis.xlsx
+++ b/updated_generic_infra_kpis.xlsx
@@ -1695,14 +1695,14 @@
           <t>Volume + dedup ratio per rule: query .ds-bridge-alerts-netcool-default-* STATS volume = COUNT(*), correlated_via = COUNT_DISTINCT(join_key) BY rule_name. Rank descending. For the false-positive dimension, need an analyst-feedback field (kibana.alert.workflow_status or a Netcool resolution-reason field). If absent, mark rules with high volume but zero incident conversion (join with servicenow-incidents-*) as noise candidates.</t>
         </is>
       </c>
-      <c r="T11" s="10" t="inlineStr">
-        <is>
-          <t>YES (volume side)</t>
+      <c r="T11" s="11" t="inlineStr">
+        <is>
+          <t>NO — requires AI/ML pipeline</t>
         </is>
       </c>
       <c r="U11" s="9" t="inlineStr">
         <is>
-          <t>'Noise Reduction — Top Alert Sources (24h, by index)' datatable ranks raw alert sources by COUNT(*) in the last 24 hours. Volume side only — the false-positive rate dimension would require an analyst-feedback field on the Netcool records (e.g. kibana.alert.workflow_status or a resolution-reason field), which is not currently present.</t>
+          <t>Not achievable as a Kibana Lens panel. The original KPI is classified as an AI Insight metric — 'AI-ranked candidates for alert tuning, dedup, or suppression'. Requires: (1) a stable rule.name / alert.rule.name on the Netcool stream (not indexed), (2) duplicate-rate from Netcool ObjectServer rule outcomes (not indexed), (3) analyst-workflow / ignored-rate field (not indexed), (4) alert-to-incident conversion join (no correlation key), (5) analyst false-positive feedback (not indexed). Even with all five, the 'AI ranking' implies an Elastic ML anomaly-detection or supervised classifier job — a Lens panel can display the ML output but cannot compute the score. Replaced the earlier placeholder table with a markdown documenting the gap and the shortest remediation path. Interim substitute already on the dashboard: the 'Alert Volume Trend' line chart surfaces spikes that would score highest for tuning.</t>
         </is>
       </c>
     </row>
